--- a/data/2.full_abstracting/26_07_full_decisions.xlsx
+++ b/data/2.full_abstracting/26_07_full_decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2789" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82127D10-A2BC-4DF1-8629-FE5E2725BD5A}"/>
+  <xr:revisionPtr revIDLastSave="2797" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A1F853-6DE7-4613-9EF6-228DF7700D72}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic_info" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="1552">
   <si>
     <t>title</t>
   </si>
@@ -4672,6 +4672,33 @@
   </si>
   <si>
     <t>preferenceforhumanvsdigital excluded because not continuous</t>
+  </si>
+  <si>
+    <t>Jaggy et al.</t>
+  </si>
+  <si>
+    <t>Hopwood</t>
+  </si>
+  <si>
+    <t>Ntumi et al.</t>
+  </si>
+  <si>
+    <t>Allemand et al.</t>
+  </si>
+  <si>
+    <t>Santiago-Rosario et al.</t>
+  </si>
+  <si>
+    <t>Springstein et al.</t>
+  </si>
+  <si>
+    <t>Feraco et al.</t>
+  </si>
+  <si>
+    <t>Scurtu-Tura et al.</t>
+  </si>
+  <si>
+    <t>changegoals; volitionalchange</t>
   </si>
 </sst>
 </file>
@@ -4728,7 +4755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4739,6 +4766,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -5229,6 +5257,9 @@
       <c r="I3" s="5" t="s">
         <v>1513</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>1544</v>
+      </c>
       <c r="K3" s="5">
         <v>2026</v>
       </c>
@@ -5275,6 +5306,9 @@
       <c r="I4" s="5" t="s">
         <v>1515</v>
       </c>
+      <c r="J4" s="5" t="s">
+        <v>1545</v>
+      </c>
       <c r="K4" s="5">
         <v>2026</v>
       </c>
@@ -5317,6 +5351,9 @@
       <c r="I5" s="5" t="s">
         <v>1517</v>
       </c>
+      <c r="J5" s="5" t="s">
+        <v>1546</v>
+      </c>
       <c r="K5" s="5">
         <v>2026</v>
       </c>
@@ -5325,6 +5362,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>1455</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>1551</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>1486</v>
@@ -5393,6 +5433,9 @@
       <c r="I6" s="5" t="s">
         <v>1519</v>
       </c>
+      <c r="J6" s="5" t="s">
+        <v>1547</v>
+      </c>
       <c r="K6" s="5">
         <v>2026</v>
       </c>
@@ -5434,6 +5477,9 @@
       </c>
       <c r="I7" s="5" t="s">
         <v>1521</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>1548</v>
       </c>
       <c r="K7" s="5">
         <v>2026</v>
@@ -5514,6 +5560,9 @@
       <c r="I8" s="5" t="s">
         <v>1523</v>
       </c>
+      <c r="J8" s="5" t="s">
+        <v>1549</v>
+      </c>
       <c r="K8" s="5">
         <v>2026</v>
       </c>
@@ -5566,6 +5615,9 @@
       <c r="I9" s="5" t="s">
         <v>1525</v>
       </c>
+      <c r="J9" s="5" t="s">
+        <v>1550</v>
+      </c>
       <c r="K9" s="5">
         <v>2026</v>
       </c>
@@ -5606,6 +5658,9 @@
       <c r="I10" s="5" t="s">
         <v>1526</v>
       </c>
+      <c r="J10" s="5" t="s">
+        <v>1543</v>
+      </c>
       <c r="K10" s="5">
         <v>2026</v>
       </c>
@@ -5627,612 +5682,714 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="D12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="D13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="D14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="D15" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="D16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D19" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D24" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D31" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D38" t="str">
         <f t="shared" ref="D38:D101" si="1">B38&amp;""&amp;C38</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D42" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D43" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D44" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="45" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D45" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D46" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D47" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D49" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D50" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D54" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D55" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D57" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D58" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D60" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D61" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D62" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D63" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D65" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D66" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D67" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D68" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D69" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D70" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J72" s="8"/>
+    </row>
+    <row r="73" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D73" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J73" s="8"/>
+    </row>
+    <row r="74" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J74" s="8"/>
+    </row>
+    <row r="75" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D75" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J75" s="8"/>
+    </row>
+    <row r="76" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D76" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D77" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J77" s="8"/>
+    </row>
+    <row r="78" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D78" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J78" s="8"/>
+    </row>
+    <row r="79" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D79" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J79" s="8"/>
+    </row>
+    <row r="80" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D80" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J80" s="8"/>
+    </row>
+    <row r="81" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D81" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J81" s="8"/>
+    </row>
+    <row r="82" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D82" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J82" s="8"/>
+    </row>
+    <row r="83" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D83" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J83" s="8"/>
+    </row>
+    <row r="84" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D84" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J84" s="8"/>
+    </row>
+    <row r="85" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D85" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J85" s="8"/>
+    </row>
+    <row r="86" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D86" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D87" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J87" s="8"/>
+    </row>
+    <row r="88" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J88" s="8"/>
+    </row>
+    <row r="89" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D89" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J89" s="8"/>
+    </row>
+    <row r="90" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D90" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J90" s="8"/>
+    </row>
+    <row r="91" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D91" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J91" s="8"/>
+    </row>
+    <row r="92" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D92" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J92" s="8"/>
+    </row>
+    <row r="93" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D93" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J93" s="8"/>
+    </row>
+    <row r="94" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D94" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J94" s="8"/>
+    </row>
+    <row r="95" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D95" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J95" s="8"/>
+    </row>
+    <row r="96" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D96" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J96" s="8"/>
+    </row>
+    <row r="97" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D97" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J97" s="8"/>
+    </row>
+    <row r="98" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J98" s="8"/>
+    </row>
+    <row r="99" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J99" s="8"/>
+    </row>
+    <row r="100" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D100" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J100" s="8"/>
+    </row>
+    <row r="101" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D101" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J101" s="8"/>
+    </row>
+    <row r="102" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D102" t="str">
         <f t="shared" ref="D102:D112" si="2">B102&amp;""&amp;C102</f>
         <v/>
       </c>
-    </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J102" s="8"/>
+    </row>
+    <row r="103" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J103" s="8"/>
+    </row>
+    <row r="104" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D104" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J104" s="8"/>
+    </row>
+    <row r="105" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D105" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J105" s="8"/>
+    </row>
+    <row r="106" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D106" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J106" s="8"/>
+    </row>
+    <row r="107" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D107" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J107" s="8"/>
+    </row>
+    <row r="108" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D108" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J108" s="8"/>
+    </row>
+    <row r="109" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D109" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J109" s="8"/>
+    </row>
+    <row r="110" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D110" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J110" s="8"/>
+    </row>
+    <row r="111" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D111" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J111" s="8"/>
+    </row>
+    <row r="112" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D112" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
+      <c r="J112" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
